--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648237</v>
+        <v>121648242</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312550</v>
+        <v>312672</v>
       </c>
       <c r="R2" t="n">
-        <v>6522685</v>
+        <v>6522520</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648242</v>
+        <v>121648252</v>
       </c>
       <c r="B3" t="n">
-        <v>95699</v>
+        <v>90739</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312672</v>
+        <v>312579</v>
       </c>
       <c r="R3" t="n">
-        <v>6522520</v>
+        <v>6522713</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648240</v>
+        <v>121648245</v>
       </c>
       <c r="B4" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312558</v>
+        <v>312645</v>
       </c>
       <c r="R4" t="n">
-        <v>6522549</v>
+        <v>6522700</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648252</v>
+        <v>121648237</v>
       </c>
       <c r="B5" t="n">
-        <v>90739</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312579</v>
+        <v>312550</v>
       </c>
       <c r="R5" t="n">
-        <v>6522713</v>
+        <v>6522685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648246</v>
+        <v>121648251</v>
       </c>
       <c r="B6" t="n">
-        <v>80251</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312635</v>
+        <v>312587</v>
       </c>
       <c r="R6" t="n">
-        <v>6522702</v>
+        <v>6522720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1172,17 +1192,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1200,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648239</v>
+        <v>121648250</v>
       </c>
       <c r="B7" t="n">
         <v>95699</v>
@@ -1240,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312582</v>
+        <v>312589</v>
       </c>
       <c r="R7" t="n">
-        <v>6522624</v>
+        <v>6522715</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648244</v>
+        <v>121648248</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>95699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,43 +1334,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312658</v>
+        <v>312606</v>
       </c>
       <c r="R8" t="n">
-        <v>6522615</v>
+        <v>6522665</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1393,21 +1408,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648253</v>
+        <v>121648256</v>
       </c>
       <c r="B9" t="n">
         <v>95699</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312577</v>
+        <v>312540</v>
       </c>
       <c r="R9" t="n">
-        <v>6522750</v>
+        <v>6522807</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648248</v>
+        <v>121648254</v>
       </c>
       <c r="B10" t="n">
         <v>95699</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312606</v>
+        <v>312559</v>
       </c>
       <c r="R10" t="n">
-        <v>6522665</v>
+        <v>6522791</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648257</v>
+        <v>121648238</v>
       </c>
       <c r="B11" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312539</v>
+        <v>312584</v>
       </c>
       <c r="R11" t="n">
-        <v>6522853</v>
+        <v>6522683</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1714,21 +1714,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1745,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648254</v>
+        <v>121648240</v>
       </c>
       <c r="B12" t="n">
         <v>95699</v>
@@ -1785,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312559</v>
+        <v>312558</v>
       </c>
       <c r="R12" t="n">
-        <v>6522791</v>
+        <v>6522549</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648238</v>
+        <v>121648239</v>
       </c>
       <c r="B13" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312584</v>
+        <v>312582</v>
       </c>
       <c r="R13" t="n">
-        <v>6522683</v>
+        <v>6522624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648255</v>
+        <v>121648244</v>
       </c>
       <c r="B14" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,38 +1946,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312569</v>
+        <v>312658</v>
       </c>
       <c r="R14" t="n">
-        <v>6522797</v>
+        <v>6522615</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2035,6 +2025,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648251</v>
+        <v>121648253</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>95699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,39 +2072,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312587</v>
+        <v>312577</v>
       </c>
       <c r="R15" t="n">
-        <v>6522720</v>
+        <v>6522750</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,21 +2142,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2173,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648247</v>
+        <v>121648243</v>
       </c>
       <c r="B16" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312610</v>
+        <v>312650</v>
       </c>
       <c r="R16" t="n">
-        <v>6522684</v>
+        <v>6522586</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2259,6 +2244,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648256</v>
+        <v>121648257</v>
       </c>
       <c r="B17" t="n">
         <v>95699</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312540</v>
+        <v>312539</v>
       </c>
       <c r="R17" t="n">
-        <v>6522807</v>
+        <v>6522853</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2361,6 +2361,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2377,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648243</v>
+        <v>121648241</v>
       </c>
       <c r="B18" t="n">
-        <v>90712</v>
+        <v>95699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312650</v>
+        <v>312658</v>
       </c>
       <c r="R18" t="n">
-        <v>6522586</v>
+        <v>6522494</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2463,21 +2478,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648245</v>
+        <v>121648247</v>
       </c>
       <c r="B19" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312645</v>
+        <v>312610</v>
       </c>
       <c r="R19" t="n">
-        <v>6522700</v>
+        <v>6522684</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,21 +2580,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2611,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648249</v>
+        <v>121648255</v>
       </c>
       <c r="B20" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312592</v>
+        <v>312569</v>
       </c>
       <c r="R20" t="n">
-        <v>6522709</v>
+        <v>6522797</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2713,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648241</v>
+        <v>121648249</v>
       </c>
       <c r="B21" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312658</v>
+        <v>312592</v>
       </c>
       <c r="R21" t="n">
-        <v>6522494</v>
+        <v>6522709</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648250</v>
+        <v>121648246</v>
       </c>
       <c r="B22" t="n">
-        <v>95699</v>
+        <v>80251</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312589</v>
+        <v>312635</v>
       </c>
       <c r="R22" t="n">
-        <v>6522715</v>
+        <v>6522702</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2886,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648253</v>
+        <v>121648243</v>
       </c>
       <c r="B15" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312577</v>
+        <v>312650</v>
       </c>
       <c r="R15" t="n">
-        <v>6522750</v>
+        <v>6522586</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,6 +2142,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2158,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648243</v>
+        <v>121648253</v>
       </c>
       <c r="B16" t="n">
-        <v>90712</v>
+        <v>95699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312650</v>
+        <v>312577</v>
       </c>
       <c r="R16" t="n">
-        <v>6522586</v>
+        <v>6522750</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2244,21 +2259,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648242</v>
+        <v>121648251</v>
       </c>
       <c r="B2" t="n">
-        <v>95699</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312672</v>
+        <v>312587</v>
       </c>
       <c r="R2" t="n">
-        <v>6522520</v>
+        <v>6522720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648252</v>
+        <v>121648238</v>
       </c>
       <c r="B3" t="n">
-        <v>90739</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312579</v>
+        <v>312584</v>
       </c>
       <c r="R3" t="n">
-        <v>6522713</v>
+        <v>6522683</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648245</v>
+        <v>121648253</v>
       </c>
       <c r="B4" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312645</v>
+        <v>312577</v>
       </c>
       <c r="R4" t="n">
-        <v>6522700</v>
+        <v>6522750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,21 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648237</v>
+        <v>121648247</v>
       </c>
       <c r="B5" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312550</v>
+        <v>312610</v>
       </c>
       <c r="R5" t="n">
-        <v>6522685</v>
+        <v>6522684</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648251</v>
+        <v>121648248</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>95699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312587</v>
+        <v>312606</v>
       </c>
       <c r="R6" t="n">
-        <v>6522720</v>
+        <v>6522665</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,21 +1189,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648250</v>
+        <v>121648241</v>
       </c>
       <c r="B7" t="n">
         <v>95699</v>
@@ -1260,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312589</v>
+        <v>312658</v>
       </c>
       <c r="R7" t="n">
-        <v>6522715</v>
+        <v>6522494</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648248</v>
+        <v>121648240</v>
       </c>
       <c r="B8" t="n">
         <v>95699</v>
@@ -1362,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312606</v>
+        <v>312558</v>
       </c>
       <c r="R8" t="n">
-        <v>6522665</v>
+        <v>6522549</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648256</v>
+        <v>121648254</v>
       </c>
       <c r="B9" t="n">
         <v>95699</v>
@@ -1464,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312540</v>
+        <v>312559</v>
       </c>
       <c r="R9" t="n">
-        <v>6522807</v>
+        <v>6522791</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648254</v>
+        <v>121648252</v>
       </c>
       <c r="B10" t="n">
-        <v>95699</v>
+        <v>90739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312559</v>
+        <v>312579</v>
       </c>
       <c r="R10" t="n">
-        <v>6522791</v>
+        <v>6522713</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648238</v>
+        <v>121648239</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312584</v>
+        <v>312582</v>
       </c>
       <c r="R11" t="n">
-        <v>6522683</v>
+        <v>6522624</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648240</v>
+        <v>121648250</v>
       </c>
       <c r="B12" t="n">
         <v>95699</v>
@@ -1770,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312558</v>
+        <v>312589</v>
       </c>
       <c r="R12" t="n">
-        <v>6522549</v>
+        <v>6522715</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1832,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648239</v>
+        <v>121648255</v>
       </c>
       <c r="B13" t="n">
         <v>95699</v>
@@ -1872,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312582</v>
+        <v>312569</v>
       </c>
       <c r="R13" t="n">
-        <v>6522624</v>
+        <v>6522797</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1934,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648244</v>
+        <v>121648249</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>74661</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,43 +1931,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312658</v>
+        <v>312592</v>
       </c>
       <c r="R14" t="n">
-        <v>6522615</v>
+        <v>6522709</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2025,21 +2005,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2056,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648243</v>
+        <v>121648237</v>
       </c>
       <c r="B15" t="n">
-        <v>90712</v>
+        <v>92004</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312650</v>
+        <v>312550</v>
       </c>
       <c r="R15" t="n">
-        <v>6522586</v>
+        <v>6522685</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,21 +2107,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2173,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648253</v>
+        <v>121648242</v>
       </c>
       <c r="B16" t="n">
         <v>95699</v>
@@ -2213,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312577</v>
+        <v>312672</v>
       </c>
       <c r="R16" t="n">
-        <v>6522750</v>
+        <v>6522520</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2392,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648241</v>
+        <v>121648244</v>
       </c>
       <c r="B18" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,28 +2354,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
@@ -2435,7 +2390,7 @@
         <v>312658</v>
       </c>
       <c r="R18" t="n">
-        <v>6522494</v>
+        <v>6522615</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2478,6 +2433,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648247</v>
+        <v>121648246</v>
       </c>
       <c r="B19" t="n">
-        <v>95699</v>
+        <v>80251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312610</v>
+        <v>312635</v>
       </c>
       <c r="R19" t="n">
-        <v>6522684</v>
+        <v>6522702</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,6 +2550,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2596,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648255</v>
+        <v>121648243</v>
       </c>
       <c r="B20" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312569</v>
+        <v>312650</v>
       </c>
       <c r="R20" t="n">
-        <v>6522797</v>
+        <v>6522586</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2682,6 +2667,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648249</v>
+        <v>121648256</v>
       </c>
       <c r="B21" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312592</v>
+        <v>312540</v>
       </c>
       <c r="R21" t="n">
-        <v>6522709</v>
+        <v>6522807</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648246</v>
+        <v>121648245</v>
       </c>
       <c r="B22" t="n">
-        <v>80251</v>
+        <v>74661</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312635</v>
+        <v>312645</v>
       </c>
       <c r="R22" t="n">
-        <v>6522702</v>
+        <v>6522700</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648251</v>
+        <v>121648238</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312587</v>
+        <v>312584</v>
       </c>
       <c r="R2" t="n">
-        <v>6522720</v>
+        <v>6522683</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648238</v>
+        <v>121648251</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312584</v>
+        <v>312587</v>
       </c>
       <c r="R3" t="n">
-        <v>6522683</v>
+        <v>6522720</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648244</v>
+        <v>121648246</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>80251</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,43 +2354,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312658</v>
+        <v>312635</v>
       </c>
       <c r="R18" t="n">
-        <v>6522615</v>
+        <v>6522702</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2436,17 +2431,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2464,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648246</v>
+        <v>121648244</v>
       </c>
       <c r="B19" t="n">
-        <v>80251</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,38 +2471,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312635</v>
+        <v>312658</v>
       </c>
       <c r="R19" t="n">
-        <v>6522702</v>
+        <v>6522615</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648238</v>
+        <v>121648249</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>74661</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312584</v>
+        <v>312592</v>
       </c>
       <c r="R2" t="n">
-        <v>6522683</v>
+        <v>6522709</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648251</v>
+        <v>121648241</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>95699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312587</v>
+        <v>312658</v>
       </c>
       <c r="R3" t="n">
-        <v>6522720</v>
+        <v>6522494</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,21 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648253</v>
+        <v>121648240</v>
       </c>
       <c r="B4" t="n">
         <v>95699</v>
@@ -939,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312577</v>
+        <v>312558</v>
       </c>
       <c r="R4" t="n">
-        <v>6522750</v>
+        <v>6522549</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648247</v>
+        <v>121648237</v>
       </c>
       <c r="B5" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312610</v>
+        <v>312550</v>
       </c>
       <c r="R5" t="n">
-        <v>6522684</v>
+        <v>6522685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648248</v>
+        <v>121648244</v>
       </c>
       <c r="B6" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312606</v>
+        <v>312658</v>
       </c>
       <c r="R6" t="n">
-        <v>6522665</v>
+        <v>6522615</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,6 +1174,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648241</v>
+        <v>121648248</v>
       </c>
       <c r="B7" t="n">
         <v>95699</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312658</v>
+        <v>312606</v>
       </c>
       <c r="R7" t="n">
-        <v>6522494</v>
+        <v>6522665</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648240</v>
+        <v>121648250</v>
       </c>
       <c r="B8" t="n">
         <v>95699</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312558</v>
+        <v>312589</v>
       </c>
       <c r="R8" t="n">
-        <v>6522549</v>
+        <v>6522715</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648254</v>
+        <v>121648246</v>
       </c>
       <c r="B9" t="n">
-        <v>95699</v>
+        <v>80251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312559</v>
+        <v>312635</v>
       </c>
       <c r="R9" t="n">
-        <v>6522791</v>
+        <v>6522702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,6 +1495,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1511,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648252</v>
+        <v>121648255</v>
       </c>
       <c r="B10" t="n">
-        <v>90739</v>
+        <v>95699</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312579</v>
+        <v>312569</v>
       </c>
       <c r="R10" t="n">
-        <v>6522713</v>
+        <v>6522797</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648239</v>
+        <v>121648256</v>
       </c>
       <c r="B11" t="n">
         <v>95699</v>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312582</v>
+        <v>312540</v>
       </c>
       <c r="R11" t="n">
-        <v>6522624</v>
+        <v>6522807</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648250</v>
+        <v>121648247</v>
       </c>
       <c r="B12" t="n">
         <v>95699</v>
@@ -1755,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312589</v>
+        <v>312610</v>
       </c>
       <c r="R12" t="n">
-        <v>6522715</v>
+        <v>6522684</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648255</v>
+        <v>121648257</v>
       </c>
       <c r="B13" t="n">
         <v>95699</v>
@@ -1857,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312569</v>
+        <v>312539</v>
       </c>
       <c r="R13" t="n">
-        <v>6522797</v>
+        <v>6522853</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1903,6 +1918,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1919,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648249</v>
+        <v>121648254</v>
       </c>
       <c r="B14" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312592</v>
+        <v>312559</v>
       </c>
       <c r="R14" t="n">
-        <v>6522709</v>
+        <v>6522791</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2021,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648237</v>
+        <v>121648245</v>
       </c>
       <c r="B15" t="n">
-        <v>92004</v>
+        <v>74661</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312550</v>
+        <v>312645</v>
       </c>
       <c r="R15" t="n">
-        <v>6522685</v>
+        <v>6522700</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2107,6 +2137,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2123,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648242</v>
+        <v>121648239</v>
       </c>
       <c r="B16" t="n">
         <v>95699</v>
@@ -2163,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312672</v>
+        <v>312582</v>
       </c>
       <c r="R16" t="n">
-        <v>6522520</v>
+        <v>6522624</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2225,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648257</v>
+        <v>121648243</v>
       </c>
       <c r="B17" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312539</v>
+        <v>312650</v>
       </c>
       <c r="R17" t="n">
-        <v>6522853</v>
+        <v>6522586</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2314,17 +2359,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2342,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648246</v>
+        <v>121648253</v>
       </c>
       <c r="B18" t="n">
-        <v>80251</v>
+        <v>95699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312635</v>
+        <v>312577</v>
       </c>
       <c r="R18" t="n">
-        <v>6522702</v>
+        <v>6522750</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2428,21 +2473,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2459,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648244</v>
+        <v>121648251</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,20 +2501,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2495,7 +2525,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2504,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312658</v>
+        <v>312587</v>
       </c>
       <c r="R19" t="n">
-        <v>6522615</v>
+        <v>6522720</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2581,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648243</v>
+        <v>121648252</v>
       </c>
       <c r="B20" t="n">
-        <v>90712</v>
+        <v>90739</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312650</v>
+        <v>312579</v>
       </c>
       <c r="R20" t="n">
-        <v>6522586</v>
+        <v>6522713</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2667,21 +2697,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2698,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648256</v>
+        <v>121648238</v>
       </c>
       <c r="B21" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312540</v>
+        <v>312584</v>
       </c>
       <c r="R21" t="n">
-        <v>6522807</v>
+        <v>6522683</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2800,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648245</v>
+        <v>121648242</v>
       </c>
       <c r="B22" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312645</v>
+        <v>312672</v>
       </c>
       <c r="R22" t="n">
-        <v>6522700</v>
+        <v>6522520</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2886,21 +2901,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648249</v>
+        <v>121648255</v>
       </c>
       <c r="B2" t="n">
-        <v>74661</v>
+        <v>95699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312592</v>
+        <v>312569</v>
       </c>
       <c r="R2" t="n">
-        <v>6522709</v>
+        <v>6522797</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648241</v>
+        <v>121648242</v>
       </c>
       <c r="B3" t="n">
         <v>95699</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312658</v>
+        <v>312672</v>
       </c>
       <c r="R3" t="n">
-        <v>6522494</v>
+        <v>6522520</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648240</v>
+        <v>121648256</v>
       </c>
       <c r="B4" t="n">
         <v>95699</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312558</v>
+        <v>312540</v>
       </c>
       <c r="R4" t="n">
-        <v>6522549</v>
+        <v>6522807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648237</v>
+        <v>121648245</v>
       </c>
       <c r="B5" t="n">
-        <v>92004</v>
+        <v>74661</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312550</v>
+        <v>312645</v>
       </c>
       <c r="R5" t="n">
-        <v>6522685</v>
+        <v>6522700</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,6 +1067,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1307,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648250</v>
+        <v>121648252</v>
       </c>
       <c r="B8" t="n">
-        <v>95699</v>
+        <v>90739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312589</v>
+        <v>312579</v>
       </c>
       <c r="R8" t="n">
-        <v>6522715</v>
+        <v>6522713</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648246</v>
+        <v>121648247</v>
       </c>
       <c r="B9" t="n">
-        <v>80251</v>
+        <v>95699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312635</v>
+        <v>312610</v>
       </c>
       <c r="R9" t="n">
-        <v>6522702</v>
+        <v>6522684</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,21 +1510,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648255</v>
+        <v>121648239</v>
       </c>
       <c r="B10" t="n">
         <v>95699</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312569</v>
+        <v>312582</v>
       </c>
       <c r="R10" t="n">
-        <v>6522797</v>
+        <v>6522624</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648256</v>
+        <v>121648241</v>
       </c>
       <c r="B11" t="n">
         <v>95699</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312540</v>
+        <v>312658</v>
       </c>
       <c r="R11" t="n">
-        <v>6522807</v>
+        <v>6522494</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648247</v>
+        <v>121648237</v>
       </c>
       <c r="B12" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312610</v>
+        <v>312550</v>
       </c>
       <c r="R12" t="n">
-        <v>6522684</v>
+        <v>6522685</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648257</v>
+        <v>121648254</v>
       </c>
       <c r="B13" t="n">
         <v>95699</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312539</v>
+        <v>312559</v>
       </c>
       <c r="R13" t="n">
-        <v>6522853</v>
+        <v>6522791</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1918,21 +1918,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1949,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648254</v>
+        <v>121648246</v>
       </c>
       <c r="B14" t="n">
-        <v>95699</v>
+        <v>80251</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312559</v>
+        <v>312635</v>
       </c>
       <c r="R14" t="n">
-        <v>6522791</v>
+        <v>6522702</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2035,6 +2020,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648245</v>
+        <v>121648251</v>
       </c>
       <c r="B15" t="n">
-        <v>74661</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,34 +2067,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312645</v>
+        <v>312587</v>
       </c>
       <c r="R15" t="n">
-        <v>6522700</v>
+        <v>6522720</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648239</v>
+        <v>121648243</v>
       </c>
       <c r="B16" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312582</v>
+        <v>312650</v>
       </c>
       <c r="R16" t="n">
-        <v>6522624</v>
+        <v>6522586</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2254,6 +2259,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2270,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648243</v>
+        <v>121648253</v>
       </c>
       <c r="B17" t="n">
-        <v>90712</v>
+        <v>95699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312650</v>
+        <v>312577</v>
       </c>
       <c r="R17" t="n">
-        <v>6522586</v>
+        <v>6522750</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2356,21 +2376,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2387,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648253</v>
+        <v>121648240</v>
       </c>
       <c r="B18" t="n">
         <v>95699</v>
@@ -2427,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312577</v>
+        <v>312558</v>
       </c>
       <c r="R18" t="n">
-        <v>6522750</v>
+        <v>6522549</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2489,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648251</v>
+        <v>121648238</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>92004</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,39 +2510,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312587</v>
+        <v>312584</v>
       </c>
       <c r="R19" t="n">
-        <v>6522720</v>
+        <v>6522683</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,21 +2580,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2611,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648252</v>
+        <v>121648250</v>
       </c>
       <c r="B20" t="n">
-        <v>90739</v>
+        <v>95699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312579</v>
+        <v>312589</v>
       </c>
       <c r="R20" t="n">
-        <v>6522713</v>
+        <v>6522715</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2713,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648238</v>
+        <v>121648257</v>
       </c>
       <c r="B21" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312584</v>
+        <v>312539</v>
       </c>
       <c r="R21" t="n">
-        <v>6522683</v>
+        <v>6522853</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,6 +2784,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648242</v>
+        <v>121648249</v>
       </c>
       <c r="B22" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312672</v>
+        <v>312592</v>
       </c>
       <c r="R22" t="n">
-        <v>6522520</v>
+        <v>6522709</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648255</v>
+        <v>121648252</v>
       </c>
       <c r="B2" t="n">
-        <v>95699</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312569</v>
+        <v>312579</v>
       </c>
       <c r="R2" t="n">
-        <v>6522797</v>
+        <v>6522713</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648242</v>
+        <v>121648249</v>
       </c>
       <c r="B3" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312672</v>
+        <v>312592</v>
       </c>
       <c r="R3" t="n">
-        <v>6522520</v>
+        <v>6522709</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648256</v>
+        <v>121648254</v>
       </c>
       <c r="B4" t="n">
         <v>95699</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312540</v>
+        <v>312559</v>
       </c>
       <c r="R4" t="n">
-        <v>6522807</v>
+        <v>6522791</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648244</v>
+        <v>121648255</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>95699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,43 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312658</v>
+        <v>312569</v>
       </c>
       <c r="R6" t="n">
-        <v>6522615</v>
+        <v>6522797</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,21 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648248</v>
+        <v>121648246</v>
       </c>
       <c r="B7" t="n">
-        <v>95699</v>
+        <v>80251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312606</v>
+        <v>312635</v>
       </c>
       <c r="R7" t="n">
-        <v>6522665</v>
+        <v>6522702</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1306,6 +1286,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648252</v>
+        <v>121648238</v>
       </c>
       <c r="B8" t="n">
-        <v>90739</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312579</v>
+        <v>312584</v>
       </c>
       <c r="R8" t="n">
-        <v>6522713</v>
+        <v>6522683</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648247</v>
+        <v>121648240</v>
       </c>
       <c r="B9" t="n">
         <v>95699</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312610</v>
+        <v>312558</v>
       </c>
       <c r="R9" t="n">
-        <v>6522684</v>
+        <v>6522549</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648239</v>
+        <v>121648242</v>
       </c>
       <c r="B10" t="n">
         <v>95699</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312582</v>
+        <v>312672</v>
       </c>
       <c r="R10" t="n">
-        <v>6522624</v>
+        <v>6522520</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648241</v>
+        <v>121648237</v>
       </c>
       <c r="B11" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312658</v>
+        <v>312550</v>
       </c>
       <c r="R11" t="n">
-        <v>6522494</v>
+        <v>6522685</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648237</v>
+        <v>121648247</v>
       </c>
       <c r="B12" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312550</v>
+        <v>312610</v>
       </c>
       <c r="R12" t="n">
-        <v>6522685</v>
+        <v>6522684</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1832,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648254</v>
+        <v>121648248</v>
       </c>
       <c r="B13" t="n">
         <v>95699</v>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312559</v>
+        <v>312606</v>
       </c>
       <c r="R13" t="n">
-        <v>6522791</v>
+        <v>6522665</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648246</v>
+        <v>121648239</v>
       </c>
       <c r="B14" t="n">
-        <v>80251</v>
+        <v>95699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312635</v>
+        <v>312582</v>
       </c>
       <c r="R14" t="n">
-        <v>6522702</v>
+        <v>6522624</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2020,21 +2015,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2051,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648251</v>
+        <v>121648253</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>95699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312587</v>
+        <v>312577</v>
       </c>
       <c r="R15" t="n">
-        <v>6522720</v>
+        <v>6522750</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,21 +2117,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2173,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648243</v>
+        <v>121648250</v>
       </c>
       <c r="B16" t="n">
-        <v>90712</v>
+        <v>95699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312650</v>
+        <v>312589</v>
       </c>
       <c r="R16" t="n">
-        <v>6522586</v>
+        <v>6522715</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2259,21 +2219,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2290,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648253</v>
+        <v>121648256</v>
       </c>
       <c r="B17" t="n">
         <v>95699</v>
@@ -2330,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312577</v>
+        <v>312540</v>
       </c>
       <c r="R17" t="n">
-        <v>6522750</v>
+        <v>6522807</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648240</v>
+        <v>121648251</v>
       </c>
       <c r="B18" t="n">
-        <v>95699</v>
+        <v>5193</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,34 +2353,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312558</v>
+        <v>312587</v>
       </c>
       <c r="R18" t="n">
-        <v>6522549</v>
+        <v>6522720</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2478,6 +2428,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648238</v>
+        <v>121648257</v>
       </c>
       <c r="B19" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312584</v>
+        <v>312539</v>
       </c>
       <c r="R19" t="n">
-        <v>6522683</v>
+        <v>6522853</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,6 +2545,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2596,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648250</v>
+        <v>121648241</v>
       </c>
       <c r="B20" t="n">
         <v>95699</v>
@@ -2636,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312589</v>
+        <v>312658</v>
       </c>
       <c r="R20" t="n">
-        <v>6522715</v>
+        <v>6522494</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2698,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648257</v>
+        <v>121648244</v>
       </c>
       <c r="B21" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,38 +2690,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312539</v>
+        <v>312658</v>
       </c>
       <c r="R21" t="n">
-        <v>6522853</v>
+        <v>6522615</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2787,17 +2772,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2815,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648249</v>
+        <v>121648243</v>
       </c>
       <c r="B22" t="n">
-        <v>74661</v>
+        <v>90712</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>4660</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312592</v>
+        <v>312650</v>
       </c>
       <c r="R22" t="n">
-        <v>6522709</v>
+        <v>6522586</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2886,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648252</v>
+        <v>121648246</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>80251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>230185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312579</v>
+        <v>312635</v>
       </c>
       <c r="R2" t="n">
-        <v>6522713</v>
+        <v>6522702</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648249</v>
+        <v>121648244</v>
       </c>
       <c r="B3" t="n">
-        <v>74661</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312592</v>
+        <v>312658</v>
       </c>
       <c r="R3" t="n">
-        <v>6522709</v>
+        <v>6522615</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,6 +883,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648254</v>
+        <v>121648245</v>
       </c>
       <c r="B4" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312559</v>
+        <v>312645</v>
       </c>
       <c r="R4" t="n">
-        <v>6522791</v>
+        <v>6522700</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,6 +1000,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648245</v>
+        <v>121648237</v>
       </c>
       <c r="B5" t="n">
-        <v>74661</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312645</v>
+        <v>312550</v>
       </c>
       <c r="R5" t="n">
-        <v>6522700</v>
+        <v>6522685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,21 +1117,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1098,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648255</v>
+        <v>121648241</v>
       </c>
       <c r="B6" t="n">
         <v>95699</v>
@@ -1138,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312569</v>
+        <v>312658</v>
       </c>
       <c r="R6" t="n">
-        <v>6522797</v>
+        <v>6522494</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648246</v>
+        <v>121648256</v>
       </c>
       <c r="B7" t="n">
-        <v>80251</v>
+        <v>95699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312635</v>
+        <v>312540</v>
       </c>
       <c r="R7" t="n">
-        <v>6522702</v>
+        <v>6522807</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,21 +1321,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1317,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648238</v>
+        <v>121648248</v>
       </c>
       <c r="B8" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312584</v>
+        <v>312606</v>
       </c>
       <c r="R8" t="n">
-        <v>6522683</v>
+        <v>6522665</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648240</v>
+        <v>121648257</v>
       </c>
       <c r="B9" t="n">
         <v>95699</v>
@@ -1459,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312558</v>
+        <v>312539</v>
       </c>
       <c r="R9" t="n">
-        <v>6522549</v>
+        <v>6522853</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,6 +1525,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1521,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648242</v>
+        <v>121648252</v>
       </c>
       <c r="B10" t="n">
-        <v>95699</v>
+        <v>90739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312672</v>
+        <v>312579</v>
       </c>
       <c r="R10" t="n">
-        <v>6522520</v>
+        <v>6522713</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648237</v>
+        <v>121648253</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>95699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312550</v>
+        <v>312577</v>
       </c>
       <c r="R11" t="n">
-        <v>6522685</v>
+        <v>6522750</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1725,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648247</v>
+        <v>121648254</v>
       </c>
       <c r="B12" t="n">
         <v>95699</v>
@@ -1765,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312610</v>
+        <v>312559</v>
       </c>
       <c r="R12" t="n">
-        <v>6522684</v>
+        <v>6522791</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1827,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648248</v>
+        <v>121648240</v>
       </c>
       <c r="B13" t="n">
         <v>95699</v>
@@ -1867,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312606</v>
+        <v>312558</v>
       </c>
       <c r="R13" t="n">
-        <v>6522665</v>
+        <v>6522549</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1929,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648239</v>
+        <v>121648238</v>
       </c>
       <c r="B14" t="n">
-        <v>95699</v>
+        <v>92004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312582</v>
+        <v>312584</v>
       </c>
       <c r="R14" t="n">
-        <v>6522624</v>
+        <v>6522683</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2031,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648253</v>
+        <v>121648251</v>
       </c>
       <c r="B15" t="n">
-        <v>95699</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,34 +2082,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312577</v>
+        <v>312587</v>
       </c>
       <c r="R15" t="n">
-        <v>6522750</v>
+        <v>6522720</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2117,6 +2157,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2133,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648250</v>
+        <v>121648255</v>
       </c>
       <c r="B16" t="n">
         <v>95699</v>
@@ -2173,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312589</v>
+        <v>312569</v>
       </c>
       <c r="R16" t="n">
-        <v>6522715</v>
+        <v>6522797</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2235,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648256</v>
+        <v>121648242</v>
       </c>
       <c r="B17" t="n">
         <v>95699</v>
@@ -2275,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312540</v>
+        <v>312672</v>
       </c>
       <c r="R17" t="n">
-        <v>6522807</v>
+        <v>6522520</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2337,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648251</v>
+        <v>121648239</v>
       </c>
       <c r="B18" t="n">
-        <v>5193</v>
+        <v>95699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,39 +2408,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312587</v>
+        <v>312582</v>
       </c>
       <c r="R18" t="n">
-        <v>6522720</v>
+        <v>6522624</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2428,21 +2478,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2459,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648257</v>
+        <v>121648243</v>
       </c>
       <c r="B19" t="n">
-        <v>95699</v>
+        <v>90712</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312539</v>
+        <v>312650</v>
       </c>
       <c r="R19" t="n">
-        <v>6522853</v>
+        <v>6522586</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2548,17 +2583,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2576,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648241</v>
+        <v>121648249</v>
       </c>
       <c r="B20" t="n">
-        <v>95699</v>
+        <v>74661</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312658</v>
+        <v>312592</v>
       </c>
       <c r="R20" t="n">
-        <v>6522494</v>
+        <v>6522709</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2678,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648244</v>
+        <v>121648247</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>95699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,43 +2725,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312658</v>
+        <v>312610</v>
       </c>
       <c r="R21" t="n">
-        <v>6522615</v>
+        <v>6522684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2769,21 +2799,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2800,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648243</v>
+        <v>121648250</v>
       </c>
       <c r="B22" t="n">
-        <v>90712</v>
+        <v>95699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312650</v>
+        <v>312589</v>
       </c>
       <c r="R22" t="n">
-        <v>6522586</v>
+        <v>6522715</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2886,21 +2901,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648246</v>
+        <v>121648242</v>
       </c>
       <c r="B2" t="n">
-        <v>80251</v>
+        <v>95717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312635</v>
+        <v>312672</v>
       </c>
       <c r="R2" t="n">
-        <v>6522702</v>
+        <v>6522520</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648244</v>
+        <v>121648247</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>95717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312658</v>
+        <v>312610</v>
       </c>
       <c r="R3" t="n">
-        <v>6522615</v>
+        <v>6522684</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,21 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648245</v>
+        <v>121648240</v>
       </c>
       <c r="B4" t="n">
-        <v>74661</v>
+        <v>95717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312645</v>
+        <v>312558</v>
       </c>
       <c r="R4" t="n">
-        <v>6522700</v>
+        <v>6522549</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,21 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648237</v>
+        <v>121648255</v>
       </c>
       <c r="B5" t="n">
-        <v>92004</v>
+        <v>95717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312550</v>
+        <v>312569</v>
       </c>
       <c r="R5" t="n">
-        <v>6522685</v>
+        <v>6522797</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648241</v>
+        <v>121648254</v>
       </c>
       <c r="B6" t="n">
-        <v>95699</v>
+        <v>95717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312658</v>
+        <v>312559</v>
       </c>
       <c r="R6" t="n">
-        <v>6522494</v>
+        <v>6522791</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648256</v>
+        <v>121648250</v>
       </c>
       <c r="B7" t="n">
-        <v>95699</v>
+        <v>95717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312540</v>
+        <v>312589</v>
       </c>
       <c r="R7" t="n">
-        <v>6522807</v>
+        <v>6522715</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648248</v>
+        <v>121648256</v>
       </c>
       <c r="B8" t="n">
-        <v>95699</v>
+        <v>95717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312606</v>
+        <v>312540</v>
       </c>
       <c r="R8" t="n">
-        <v>6522665</v>
+        <v>6522807</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648257</v>
+        <v>121648237</v>
       </c>
       <c r="B9" t="n">
-        <v>95699</v>
+        <v>92018</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312539</v>
+        <v>312550</v>
       </c>
       <c r="R9" t="n">
-        <v>6522853</v>
+        <v>6522685</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,21 +1475,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648252</v>
+        <v>121648248</v>
       </c>
       <c r="B10" t="n">
-        <v>90739</v>
+        <v>95717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312579</v>
+        <v>312606</v>
       </c>
       <c r="R10" t="n">
-        <v>6522713</v>
+        <v>6522665</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648253</v>
+        <v>121648238</v>
       </c>
       <c r="B11" t="n">
-        <v>95699</v>
+        <v>92018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312577</v>
+        <v>312584</v>
       </c>
       <c r="R11" t="n">
-        <v>6522750</v>
+        <v>6522683</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648254</v>
+        <v>121648251</v>
       </c>
       <c r="B12" t="n">
-        <v>95699</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,34 +1711,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312559</v>
+        <v>312587</v>
       </c>
       <c r="R12" t="n">
-        <v>6522791</v>
+        <v>6522720</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,6 +1786,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1862,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648240</v>
+        <v>121648245</v>
       </c>
       <c r="B13" t="n">
-        <v>95699</v>
+        <v>74674</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312558</v>
+        <v>312645</v>
       </c>
       <c r="R13" t="n">
-        <v>6522549</v>
+        <v>6522700</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1948,6 +1903,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1964,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648238</v>
+        <v>121648243</v>
       </c>
       <c r="B14" t="n">
-        <v>92004</v>
+        <v>90726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312584</v>
+        <v>312650</v>
       </c>
       <c r="R14" t="n">
-        <v>6522683</v>
+        <v>6522586</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2050,6 +2020,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2066,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648251</v>
+        <v>121648257</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>95717</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,39 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312587</v>
+        <v>312539</v>
       </c>
       <c r="R15" t="n">
-        <v>6522720</v>
+        <v>6522853</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2160,17 +2140,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2188,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648255</v>
+        <v>121648249</v>
       </c>
       <c r="B16" t="n">
-        <v>95699</v>
+        <v>74674</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312569</v>
+        <v>312592</v>
       </c>
       <c r="R16" t="n">
-        <v>6522797</v>
+        <v>6522709</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648242</v>
+        <v>121648252</v>
       </c>
       <c r="B17" t="n">
-        <v>95699</v>
+        <v>90753</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312672</v>
+        <v>312579</v>
       </c>
       <c r="R17" t="n">
-        <v>6522520</v>
+        <v>6522713</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648239</v>
+        <v>121648246</v>
       </c>
       <c r="B18" t="n">
-        <v>95699</v>
+        <v>80264</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312582</v>
+        <v>312635</v>
       </c>
       <c r="R18" t="n">
-        <v>6522624</v>
+        <v>6522702</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2478,6 +2458,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648243</v>
+        <v>121648239</v>
       </c>
       <c r="B19" t="n">
-        <v>90712</v>
+        <v>95717</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312650</v>
+        <v>312582</v>
       </c>
       <c r="R19" t="n">
-        <v>6522586</v>
+        <v>6522624</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,21 +2575,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2611,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648249</v>
+        <v>121648244</v>
       </c>
       <c r="B20" t="n">
-        <v>74661</v>
+        <v>57381</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,38 +2603,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312592</v>
+        <v>312658</v>
       </c>
       <c r="R20" t="n">
-        <v>6522709</v>
+        <v>6522615</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2697,6 +2682,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648247</v>
+        <v>121648253</v>
       </c>
       <c r="B21" t="n">
-        <v>95699</v>
+        <v>95717</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312610</v>
+        <v>312577</v>
       </c>
       <c r="R21" t="n">
-        <v>6522684</v>
+        <v>6522750</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648250</v>
+        <v>121648241</v>
       </c>
       <c r="B22" t="n">
-        <v>95699</v>
+        <v>95717</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312589</v>
+        <v>312658</v>
       </c>
       <c r="R22" t="n">
-        <v>6522715</v>
+        <v>6522494</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648243</v>
+        <v>121648257</v>
       </c>
       <c r="B14" t="n">
-        <v>90726</v>
+        <v>95717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312650</v>
+        <v>312539</v>
       </c>
       <c r="R14" t="n">
-        <v>6522586</v>
+        <v>6522853</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2023,17 +2023,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648257</v>
+        <v>121648243</v>
       </c>
       <c r="B15" t="n">
-        <v>95717</v>
+        <v>90726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312539</v>
+        <v>312650</v>
       </c>
       <c r="R15" t="n">
-        <v>6522853</v>
+        <v>6522586</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648242</v>
+        <v>121648249</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
+        <v>74676</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312672</v>
+        <v>312592</v>
       </c>
       <c r="R2" t="n">
-        <v>6522520</v>
+        <v>6522709</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648247</v>
+        <v>121648248</v>
       </c>
       <c r="B3" t="n">
-        <v>95717</v>
+        <v>95722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312610</v>
+        <v>312606</v>
       </c>
       <c r="R3" t="n">
-        <v>6522684</v>
+        <v>6522665</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648240</v>
+        <v>121648257</v>
       </c>
       <c r="B4" t="n">
-        <v>95717</v>
+        <v>95722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312558</v>
+        <v>312539</v>
       </c>
       <c r="R4" t="n">
-        <v>6522549</v>
+        <v>6522853</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648255</v>
+        <v>121648252</v>
       </c>
       <c r="B5" t="n">
-        <v>95717</v>
+        <v>90755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312569</v>
+        <v>312579</v>
       </c>
       <c r="R5" t="n">
-        <v>6522797</v>
+        <v>6522713</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648254</v>
+        <v>121648255</v>
       </c>
       <c r="B6" t="n">
-        <v>95717</v>
+        <v>95722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312559</v>
+        <v>312569</v>
       </c>
       <c r="R6" t="n">
-        <v>6522791</v>
+        <v>6522797</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648250</v>
+        <v>121648238</v>
       </c>
       <c r="B7" t="n">
-        <v>95717</v>
+        <v>92020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312589</v>
+        <v>312584</v>
       </c>
       <c r="R7" t="n">
-        <v>6522715</v>
+        <v>6522683</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648256</v>
+        <v>121648250</v>
       </c>
       <c r="B8" t="n">
-        <v>95717</v>
+        <v>95722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312540</v>
+        <v>312589</v>
       </c>
       <c r="R8" t="n">
-        <v>6522807</v>
+        <v>6522715</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648237</v>
+        <v>121648253</v>
       </c>
       <c r="B9" t="n">
-        <v>92018</v>
+        <v>95722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312550</v>
+        <v>312577</v>
       </c>
       <c r="R9" t="n">
-        <v>6522685</v>
+        <v>6522750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648248</v>
+        <v>121648254</v>
       </c>
       <c r="B10" t="n">
-        <v>95717</v>
+        <v>95722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312606</v>
+        <v>312559</v>
       </c>
       <c r="R10" t="n">
-        <v>6522665</v>
+        <v>6522791</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648238</v>
+        <v>121648247</v>
       </c>
       <c r="B11" t="n">
-        <v>92018</v>
+        <v>95722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312584</v>
+        <v>312610</v>
       </c>
       <c r="R11" t="n">
-        <v>6522683</v>
+        <v>6522684</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648251</v>
+        <v>121648239</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>95722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,39 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312587</v>
+        <v>312582</v>
       </c>
       <c r="R12" t="n">
-        <v>6522720</v>
+        <v>6522624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1786,21 +1796,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648245</v>
+        <v>121648243</v>
       </c>
       <c r="B13" t="n">
-        <v>74674</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312645</v>
+        <v>312650</v>
       </c>
       <c r="R13" t="n">
-        <v>6522700</v>
+        <v>6522586</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1906,17 +1901,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648257</v>
+        <v>121648245</v>
       </c>
       <c r="B14" t="n">
-        <v>95717</v>
+        <v>74676</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312539</v>
+        <v>312645</v>
       </c>
       <c r="R14" t="n">
-        <v>6522853</v>
+        <v>6522700</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2023,17 +2018,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648243</v>
+        <v>121648240</v>
       </c>
       <c r="B15" t="n">
-        <v>90726</v>
+        <v>95722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312650</v>
+        <v>312558</v>
       </c>
       <c r="R15" t="n">
-        <v>6522586</v>
+        <v>6522549</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2137,21 +2132,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2168,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648249</v>
+        <v>121648241</v>
       </c>
       <c r="B16" t="n">
-        <v>74674</v>
+        <v>95722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312592</v>
+        <v>312658</v>
       </c>
       <c r="R16" t="n">
-        <v>6522709</v>
+        <v>6522494</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2270,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648252</v>
+        <v>121648244</v>
       </c>
       <c r="B17" t="n">
-        <v>90753</v>
+        <v>57381</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,38 +2262,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312579</v>
+        <v>312658</v>
       </c>
       <c r="R17" t="n">
-        <v>6522713</v>
+        <v>6522615</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2356,6 +2341,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648246</v>
+        <v>121648256</v>
       </c>
       <c r="B18" t="n">
-        <v>80264</v>
+        <v>95722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312635</v>
+        <v>312540</v>
       </c>
       <c r="R18" t="n">
-        <v>6522702</v>
+        <v>6522807</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2458,21 +2458,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2489,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648239</v>
+        <v>121648251</v>
       </c>
       <c r="B19" t="n">
-        <v>95717</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,34 +2490,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312582</v>
+        <v>312587</v>
       </c>
       <c r="R19" t="n">
-        <v>6522624</v>
+        <v>6522720</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2575,6 +2565,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2591,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648244</v>
+        <v>121648242</v>
       </c>
       <c r="B20" t="n">
-        <v>57381</v>
+        <v>95722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,43 +2608,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312658</v>
+        <v>312672</v>
       </c>
       <c r="R20" t="n">
-        <v>6522615</v>
+        <v>6522520</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2682,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648253</v>
+        <v>121648237</v>
       </c>
       <c r="B21" t="n">
-        <v>95717</v>
+        <v>92020</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312577</v>
+        <v>312550</v>
       </c>
       <c r="R21" t="n">
-        <v>6522750</v>
+        <v>6522685</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648241</v>
+        <v>121648246</v>
       </c>
       <c r="B22" t="n">
-        <v>95717</v>
+        <v>80266</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312658</v>
+        <v>312635</v>
       </c>
       <c r="R22" t="n">
-        <v>6522494</v>
+        <v>6522702</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2886,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648249</v>
+        <v>121648257</v>
       </c>
       <c r="B2" t="n">
-        <v>74676</v>
+        <v>95729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312592</v>
+        <v>312539</v>
       </c>
       <c r="R2" t="n">
-        <v>6522709</v>
+        <v>6522853</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121648248</v>
+        <v>121648239</v>
       </c>
       <c r="B3" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312606</v>
+        <v>312582</v>
       </c>
       <c r="R3" t="n">
-        <v>6522665</v>
+        <v>6522624</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648257</v>
+        <v>121648256</v>
       </c>
       <c r="B4" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312539</v>
+        <v>312540</v>
       </c>
       <c r="R4" t="n">
-        <v>6522853</v>
+        <v>6522807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,21 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648252</v>
+        <v>121648238</v>
       </c>
       <c r="B5" t="n">
-        <v>90755</v>
+        <v>92021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312579</v>
+        <v>312584</v>
       </c>
       <c r="R5" t="n">
-        <v>6522713</v>
+        <v>6522683</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121648255</v>
+        <v>121648242</v>
       </c>
       <c r="B6" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312569</v>
+        <v>312672</v>
       </c>
       <c r="R6" t="n">
-        <v>6522797</v>
+        <v>6522520</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648238</v>
+        <v>121648243</v>
       </c>
       <c r="B7" t="n">
-        <v>92020</v>
+        <v>90729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312584</v>
+        <v>312650</v>
       </c>
       <c r="R7" t="n">
-        <v>6522683</v>
+        <v>6522586</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,6 +1286,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1302,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648250</v>
+        <v>121648254</v>
       </c>
       <c r="B8" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312589</v>
+        <v>312559</v>
       </c>
       <c r="R8" t="n">
-        <v>6522715</v>
+        <v>6522791</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648253</v>
+        <v>121648251</v>
       </c>
       <c r="B9" t="n">
-        <v>95722</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312577</v>
+        <v>312587</v>
       </c>
       <c r="R9" t="n">
-        <v>6522750</v>
+        <v>6522720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1490,6 +1510,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1506,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648254</v>
+        <v>121648237</v>
       </c>
       <c r="B10" t="n">
-        <v>95722</v>
+        <v>92021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312559</v>
+        <v>312550</v>
       </c>
       <c r="R10" t="n">
-        <v>6522791</v>
+        <v>6522685</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648247</v>
+        <v>121648245</v>
       </c>
       <c r="B11" t="n">
-        <v>95722</v>
+        <v>74676</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312610</v>
+        <v>312645</v>
       </c>
       <c r="R11" t="n">
-        <v>6522684</v>
+        <v>6522700</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1694,6 +1729,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1710,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648239</v>
+        <v>121648244</v>
       </c>
       <c r="B12" t="n">
-        <v>95722</v>
+        <v>57381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,38 +1772,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312582</v>
+        <v>312658</v>
       </c>
       <c r="R12" t="n">
-        <v>6522624</v>
+        <v>6522615</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1796,6 +1851,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1812,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648243</v>
+        <v>121648247</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>95729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1898,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312650</v>
+        <v>312610</v>
       </c>
       <c r="R13" t="n">
-        <v>6522586</v>
+        <v>6522684</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,21 +1968,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1929,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648245</v>
+        <v>121648255</v>
       </c>
       <c r="B14" t="n">
-        <v>74676</v>
+        <v>95729</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312645</v>
+        <v>312569</v>
       </c>
       <c r="R14" t="n">
-        <v>6522700</v>
+        <v>6522797</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2015,21 +2070,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2046,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648240</v>
+        <v>121648252</v>
       </c>
       <c r="B15" t="n">
-        <v>95722</v>
+        <v>90756</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312558</v>
+        <v>312579</v>
       </c>
       <c r="R15" t="n">
-        <v>6522549</v>
+        <v>6522713</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648241</v>
+        <v>121648249</v>
       </c>
       <c r="B16" t="n">
-        <v>95722</v>
+        <v>74676</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312658</v>
+        <v>312592</v>
       </c>
       <c r="R16" t="n">
-        <v>6522494</v>
+        <v>6522709</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2250,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648244</v>
+        <v>121648248</v>
       </c>
       <c r="B17" t="n">
-        <v>57381</v>
+        <v>95729</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,43 +2302,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312658</v>
+        <v>312606</v>
       </c>
       <c r="R17" t="n">
-        <v>6522615</v>
+        <v>6522665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2341,21 +2376,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2372,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648256</v>
+        <v>121648240</v>
       </c>
       <c r="B18" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312540</v>
+        <v>312558</v>
       </c>
       <c r="R18" t="n">
-        <v>6522807</v>
+        <v>6522549</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2474,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648251</v>
+        <v>121648246</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>80267</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,39 +2510,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>230185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312587</v>
+        <v>312635</v>
       </c>
       <c r="R19" t="n">
-        <v>6522720</v>
+        <v>6522702</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2568,17 +2583,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2596,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648242</v>
+        <v>121648253</v>
       </c>
       <c r="B20" t="n">
-        <v>95722</v>
+        <v>95729</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312672</v>
+        <v>312577</v>
       </c>
       <c r="R20" t="n">
-        <v>6522520</v>
+        <v>6522750</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2698,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648237</v>
+        <v>121648241</v>
       </c>
       <c r="B21" t="n">
-        <v>92020</v>
+        <v>95729</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312550</v>
+        <v>312658</v>
       </c>
       <c r="R21" t="n">
-        <v>6522685</v>
+        <v>6522494</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2800,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648246</v>
+        <v>121648250</v>
       </c>
       <c r="B22" t="n">
-        <v>80266</v>
+        <v>95729</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312635</v>
+        <v>312589</v>
       </c>
       <c r="R22" t="n">
-        <v>6522702</v>
+        <v>6522715</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2886,21 +2901,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121648257</v>
+        <v>121648252</v>
       </c>
       <c r="B2" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312539</v>
+        <v>312579</v>
       </c>
       <c r="R2" t="n">
-        <v>6522853</v>
+        <v>6522713</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,12 +775,7 @@
         <v>121648239</v>
       </c>
       <c r="B3" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121648256</v>
+        <v>121648240</v>
       </c>
       <c r="B4" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312540</v>
+        <v>312558</v>
       </c>
       <c r="R4" t="n">
-        <v>6522807</v>
+        <v>6522549</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121648238</v>
+        <v>121648241</v>
       </c>
       <c r="B5" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312584</v>
+        <v>312658</v>
       </c>
       <c r="R5" t="n">
-        <v>6522683</v>
+        <v>6522494</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,12 +1066,7 @@
         <v>121648242</v>
       </c>
       <c r="B6" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121648243</v>
+        <v>121648247</v>
       </c>
       <c r="B7" t="n">
-        <v>90729</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312650</v>
+        <v>312610</v>
       </c>
       <c r="R7" t="n">
-        <v>6522586</v>
+        <v>6522684</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,21 +1241,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1317,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121648254</v>
+        <v>121648248</v>
       </c>
       <c r="B8" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312559</v>
+        <v>312606</v>
       </c>
       <c r="R8" t="n">
-        <v>6522791</v>
+        <v>6522665</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121648251</v>
+        <v>121648250</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,39 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312587</v>
+        <v>312589</v>
       </c>
       <c r="R9" t="n">
-        <v>6522720</v>
+        <v>6522715</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1510,21 +1435,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1541,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121648237</v>
+        <v>121648253</v>
       </c>
       <c r="B10" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312550</v>
+        <v>312577</v>
       </c>
       <c r="R10" t="n">
-        <v>6522685</v>
+        <v>6522750</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1643,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121648245</v>
+        <v>121648254</v>
       </c>
       <c r="B11" t="n">
-        <v>74676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312645</v>
+        <v>312559</v>
       </c>
       <c r="R11" t="n">
-        <v>6522700</v>
+        <v>6522791</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1729,21 +1629,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1760,55 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121648244</v>
+        <v>121648255</v>
       </c>
       <c r="B12" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312658</v>
+        <v>312569</v>
       </c>
       <c r="R12" t="n">
-        <v>6522615</v>
+        <v>6522797</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,21 +1726,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1882,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121648247</v>
+        <v>121648256</v>
       </c>
       <c r="B13" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312610</v>
+        <v>312540</v>
       </c>
       <c r="R13" t="n">
-        <v>6522684</v>
+        <v>6522807</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1984,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121648255</v>
+        <v>121648257</v>
       </c>
       <c r="B14" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312569</v>
+        <v>312539</v>
       </c>
       <c r="R14" t="n">
-        <v>6522797</v>
+        <v>6522853</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,6 +1920,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2086,37 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121648252</v>
+        <v>121648237</v>
       </c>
       <c r="B15" t="n">
-        <v>90756</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312579</v>
+        <v>312550</v>
       </c>
       <c r="R15" t="n">
-        <v>6522713</v>
+        <v>6522685</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2188,37 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121648249</v>
+        <v>121648238</v>
       </c>
       <c r="B16" t="n">
-        <v>74676</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312592</v>
+        <v>312584</v>
       </c>
       <c r="R16" t="n">
-        <v>6522709</v>
+        <v>6522683</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,15 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121648248</v>
+        <v>121648243</v>
       </c>
       <c r="B17" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312606</v>
+        <v>312650</v>
       </c>
       <c r="R17" t="n">
-        <v>6522665</v>
+        <v>6522586</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2376,6 +2226,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2392,37 +2257,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121648240</v>
+        <v>121648245</v>
       </c>
       <c r="B18" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312558</v>
+        <v>312645</v>
       </c>
       <c r="R18" t="n">
-        <v>6522549</v>
+        <v>6522700</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2478,6 +2338,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,37 +2369,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121648246</v>
+        <v>121648249</v>
       </c>
       <c r="B19" t="n">
-        <v>80267</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312635</v>
+        <v>312592</v>
       </c>
       <c r="R19" t="n">
-        <v>6522702</v>
+        <v>6522709</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,21 +2450,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2611,15 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121648253</v>
+        <v>121648244</v>
       </c>
       <c r="B20" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,34 +2477,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312577</v>
+        <v>312658</v>
       </c>
       <c r="R20" t="n">
-        <v>6522750</v>
+        <v>6522615</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2697,6 +2552,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2713,15 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121648241</v>
+        <v>121648251</v>
       </c>
       <c r="B21" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,34 +2594,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312658</v>
+        <v>312587</v>
       </c>
       <c r="R21" t="n">
-        <v>6522494</v>
+        <v>6522720</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,6 +2669,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2815,15 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121648250</v>
+        <v>121648246</v>
       </c>
       <c r="B22" t="n">
-        <v>95729</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,21 +2711,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312589</v>
+        <v>312635</v>
       </c>
       <c r="R22" t="n">
-        <v>6522715</v>
+        <v>6522702</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2781,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 56336-2024 artfynd.xlsx
+++ b/artfynd/A 56336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648242</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648247</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648248</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648250</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648254</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648256</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648257</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648237</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648238</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648243</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648245</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648249</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648244</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648251</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,8 +2914,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>